--- a/xls/square_un_16_tri3_18_0.xlsx
+++ b/xls/square_un_16_tri3_18_0.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.8091937743260824</v>
+        <v>-1.810754489043491</v>
       </c>
       <c r="J16">
-        <v>-2.0152512722043907</v>
+        <v>-2.016669630589136</v>
       </c>
       <c r="K16">
-        <v>-1.011264086496287</v>
+        <v>-1.0119639771280113</v>
       </c>
     </row>
   </sheetData>
